--- a/data/kase_aix_pref_yearly.xlsx
+++ b/data/kase_aix_pref_yearly.xlsx
@@ -13009,17 +13009,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>FRHC_KZ / FRHC</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp. / Ordinary shares of Freedom Holding Corp.</t>
+          <t>Ordinary shares of Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>акции / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -13289,17 +13289,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>HSBKd / HSBK.Y</t>
+          <t>HSBK.Y</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Народный Банк Казахстана / GDRs of "Halyk Savings Bank of Kazakhstan" JSC</t>
+          <t>GDRs of "Halyk Savings Bank of Kazakhstan" JSC</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -13307,11 +13307,7 @@
           <t>US46627J3023</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>US46627J2033</t>
-        </is>
-      </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
         <v>2026</v>
@@ -13678,22 +13674,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>KO_KZ</t>
+          <t>KAP.Y</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Global Depository Receipts of NC "Kazatomprom" JSC</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US63253R2013</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -13703,7 +13699,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I378" t="n">
@@ -13713,36 +13709,32 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>KSPId / KSPI</t>
+          <t>KO_KZ</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Kaspi.kz / AMERICAN DEPOSITORY SHARES OF JSC "KASPI.KZ"</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>US48581R2058</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>US48581R1068</t>
-        </is>
-      </c>
+          <t>US1912161007</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
         <v>2026</v>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I379" t="n">
@@ -13752,22 +13744,22 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>KZAPd / KAP.Y</t>
+          <t>KSPI</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Национальная атомная компания "Казатомпром" / Global Depository Receipts of NC "Kazatomprom" JSC</t>
+          <t>AMERICAN DEPOSITORY SHARES OF JSC "KASPI.KZ"</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>US63253R2013</t>
+          <t>US48581R2058</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>

--- a/data/kase_aix_pref_yearly.xlsx
+++ b/data/kase_aix_pref_yearly.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I414"/>
+  <dimension ref="A1:I415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12056,17 +12056,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>AIRA.Y</t>
+          <t>AIRAd / AIRA.Y</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>GDRs of Air Astana JSC</t>
+          <t>Эйр Астана / GDRs of Air Astana JSC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>производные ценные бумаги / EQTY</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -12074,7 +12074,11 @@
           <t>US0090632078</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>US0090631088</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
         <v>2026</v>
@@ -12659,12 +12663,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>C_KZ</t>
+          <t>CVX_KZ</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -12674,7 +12678,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -12694,12 +12698,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>DIS_KZ</t>
+          <t>C_KZ</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -12709,7 +12713,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>US2546871060</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -12729,12 +12733,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ETHA_KZ</t>
+          <t>DIS_KZ</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>iShares Ethereum Trust ETF</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -12744,7 +12748,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>US46438R1059</t>
+          <t>US2546871060</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -12764,12 +12768,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ETHT_KZ</t>
+          <t>ETHA_KZ</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>ProShares Trust</t>
+          <t>iShares Ethereum Trust ETF</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -12779,7 +12783,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>US74349Y5713</t>
+          <t>US46438R1059</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -12799,22 +12803,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>EUA</t>
+          <t>ETHT_KZ</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Ordinary Shares of Eurasia Mining PLC</t>
+          <t>ProShares Trust</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>GB0003230421</t>
+          <t>US74349Y5713</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
@@ -12824,7 +12828,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I353" t="n">
@@ -12834,22 +12838,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>EWQ_KZ</t>
+          <t>EUA</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>iShares Inc.</t>
+          <t>Ordinary Shares of Eurasia Mining PLC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>US4642867075</t>
+          <t>GB0003230421</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -12859,7 +12863,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I354" t="n">
@@ -12869,22 +12873,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>FAR</t>
+          <t>EWQ_KZ</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Ordinary shares of Ferro-Alloy Recources LTD</t>
+          <t>iShares Inc.</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>GG00BGDYDZ69</t>
+          <t>US4642867075</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -12894,7 +12898,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I355" t="n">
@@ -12904,22 +12908,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FCX_KZ</t>
+          <t>FAR</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan Inc.</t>
+          <t>Ordinary shares of Ferro-Alloy Recources LTD</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>US35671D8570</t>
+          <t>GG00BGDYDZ69</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -12929,7 +12933,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I356" t="n">
@@ -12939,22 +12943,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>FIXP.Y</t>
+          <t>FCX_KZ</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>GDRs of Fix Price Group PLC</t>
+          <t>Freeport-McMoRan Inc.</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>US33835G2057</t>
+          <t>US35671D8570</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -12964,7 +12968,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I357" t="n">
@@ -12974,22 +12978,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>FLGB_KZ</t>
+          <t>FIXP.Y</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Franklin Templeton Investments, Inc.</t>
+          <t>GDRs of Fix Price Group PLC</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>US35473P6786</t>
+          <t>US33835G2057</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -12999,7 +13003,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I358" t="n">
@@ -13009,22 +13013,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FLGB_KZ</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Ordinary shares of Freedom Holding Corp.</t>
+          <t>Franklin Templeton Investments, Inc.</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>US3563901046</t>
+          <t>US35473P6786</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -13034,7 +13038,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I359" t="n">
@@ -13044,22 +13048,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>FXI_KZ</t>
+          <t>FRHC_KZ / FRHC</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>iShares Trust</t>
+          <t>Freedom Holding Corp. / Ordinary shares of Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>акции / EQTY</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>US4642871846</t>
+          <t>US3563901046</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -13069,7 +13073,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I360" t="n">
@@ -13079,12 +13083,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>F_KZ</t>
+          <t>FXI_KZ</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>iShares Trust</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -13094,7 +13098,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>US3453708600</t>
+          <t>US4642871846</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -13114,22 +13118,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>GB_ALTN</t>
+          <t>F_KZ</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>AltynGold plc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>акции</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>GB00BMH19X50</t>
+          <t>US3453708600</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -13149,22 +13153,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>GDX_KZ</t>
+          <t>GB_ALTN</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>VANECK ETF TRUST</t>
+          <t>AltynGold plc</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>акции</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>US92189F1066</t>
+          <t>GB00BMH19X50</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -13184,12 +13188,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>GLD_KZ</t>
+          <t>GDX_KZ</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SPDR Gold Trust</t>
+          <t>VANECK ETF TRUST</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -13199,7 +13203,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>US78463V1070</t>
+          <t>US92189F1066</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -13219,12 +13223,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>GOOG_KZ</t>
+          <t>GLD_KZ</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>ALPHABET INC.</t>
+          <t>SPDR Gold Trust</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -13234,7 +13238,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>US02079K1079</t>
+          <t>US78463V1070</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -13254,12 +13258,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>HEPSd</t>
+          <t>GOOG_KZ</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>D-MARKET Elektronik Hizmetler ve Ticaret Anonim Sirketi (Hepsiburada)</t>
+          <t>ALPHABET INC.</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -13269,7 +13273,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>US23292B1044</t>
+          <t>US02079K1079</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -13289,22 +13293,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>HSBK.Y</t>
+          <t>HEPSd</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>GDRs of "Halyk Savings Bank of Kazakhstan" JSC</t>
+          <t>D-MARKET Elektronik Hizmetler ve Ticaret Anonim Sirketi (Hepsiburada)</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>US46627J3023</t>
+          <t>US23292B1044</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -13314,7 +13318,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I367" t="n">
@@ -13324,32 +13328,36 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>HYG_KZ</t>
+          <t>HSBKd / HSBK.Y</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>BlackRock, Inc</t>
+          <t>Народный Банк Казахстана / GDRs of "Halyk Savings Bank of Kazakhstan" JSC</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>производные ценные бумаги / EQTY</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>US4642885135</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr"/>
+          <t>US46627J3023</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>US46627J2033</t>
+        </is>
+      </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
         <v>2026</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I368" t="n">
@@ -13359,12 +13367,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>IBIT_KZ</t>
+          <t>HYG_KZ</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>iShares Bitcoin Trust ETF</t>
+          <t>BlackRock, Inc</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13374,7 +13382,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>US46438F1012</t>
+          <t>US4642885135</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -13394,12 +13402,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>IBM_KZ</t>
+          <t>IBIT_KZ</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>iShares Bitcoin Trust ETF</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13409,7 +13417,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>US4592001014</t>
+          <t>US46438F1012</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -13429,12 +13437,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ICLN_KZ</t>
+          <t>IBM_KZ</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>iShares Trust</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13444,7 +13452,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>US4642882249</t>
+          <t>US4592001014</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -13464,22 +13472,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>IE_FXBF</t>
+          <t>ICLN_KZ</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>FinEx Physically Backed Funds</t>
+          <t>iShares Trust</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ценные бумаги инвестиционных фондов</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>IE00BG0C3K84</t>
+          <t>US4642882249</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -13499,22 +13507,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>IGLB_KZ</t>
+          <t>IE_FXBF</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>iShares Trust</t>
+          <t>FinEx Physically Backed Funds</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>ценные бумаги инвестиционных фондов</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>US4642895118</t>
+          <t>IE00BG0C3K84</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -13534,12 +13542,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>INTC_KZ</t>
+          <t>IGLB_KZ</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>iShares Trust</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13549,7 +13557,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>US4581401001</t>
+          <t>US4642895118</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -13569,12 +13577,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>JNJ_KZ</t>
+          <t>INTC_KZ</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13584,7 +13592,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US4581401001</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
@@ -13604,12 +13612,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>JPM_KZ</t>
+          <t>JNJ_KZ</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13619,7 +13627,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -13639,22 +13647,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>JXIR</t>
+          <t>JPM_KZ</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Ordinary Shares of Jiaxin International</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>HK0001188587</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -13664,7 +13672,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I377" t="n">
@@ -13674,12 +13682,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>KAP.Y</t>
+          <t>JXIR</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Global Depository Receipts of NC "Kazatomprom" JSC</t>
+          <t>Ordinary Shares of Jiaxin International</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -13689,7 +13697,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>US63253R2013</t>
+          <t>HK0001188587</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -13744,17 +13752,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>KSPId / KSPI</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>AMERICAN DEPOSITORY SHARES OF JSC "KASPI.KZ"</t>
+          <t>Kaspi.kz / AMERICAN DEPOSITORY SHARES OF JSC "KASPI.KZ"</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>производные ценные бумаги / EQTY</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -13762,7 +13770,11 @@
           <t>US48581R2058</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>US48581R1068</t>
+        </is>
+      </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
         <v>2026</v>
@@ -13779,22 +13791,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>LQD_KZ</t>
+          <t>KZAPd / KAP.Y</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>BlackRock, Inc</t>
+          <t>Национальная атомная компания "Казатомпром" / Global Depository Receipts of NC "Kazatomprom" JSC</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>производные ценные бумаги / EQTY</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>US4642872422</t>
+          <t>US63253R2013</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -13804,7 +13816,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I381" t="n">
@@ -13814,12 +13826,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>MA_KZ</t>
+          <t>LQD_KZ</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Mastercard, Inc.</t>
+          <t>BlackRock, Inc</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13829,7 +13841,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US4642872422</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -13849,12 +13861,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>META_KZ</t>
+          <t>MA_KZ</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Mastercard, Inc.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -13864,7 +13876,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>US30303M1027</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -13884,12 +13896,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>MRNA_KZ</t>
+          <t>META_KZ</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13899,7 +13911,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>US60770K1079</t>
+          <t>US30303M1027</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -13919,12 +13931,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MSFT_KZ</t>
+          <t>MRNA_KZ</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13934,7 +13946,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US60770K1079</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -13954,12 +13966,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>MTB_KZ</t>
+          <t>MSFT_KZ</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>M&amp;T Bank Corporation</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -13969,7 +13981,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>US55261F1049</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -13989,12 +14001,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>MU_KZ</t>
+          <t>MTB_KZ</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>M&amp;T Bank Corporation</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -14004,7 +14016,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>US5951121038</t>
+          <t>US55261F1049</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -14024,12 +14036,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>NEM_KZ</t>
+          <t>MU_KZ</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -14039,7 +14051,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>US6516391066</t>
+          <t>US5951121038</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -14059,12 +14071,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>NFLX_KZ</t>
+          <t>NEM_KZ</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Netflix, Inc</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -14074,7 +14086,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>US64110L1061</t>
+          <t>US6516391066</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -14094,12 +14106,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>NKE_KZ</t>
+          <t>NFLX_KZ</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>NIKE, Inc.</t>
+          <t>Netflix, Inc</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -14109,7 +14121,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>US6541061031</t>
+          <t>US64110L1061</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -14129,22 +14141,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>NNDQ</t>
+          <t>NKE_KZ</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>American Depositary Shares of Nanduq PLC</t>
+          <t>NIKE, Inc.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>US74735M1080</t>
+          <t>US6541061031</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -14154,7 +14166,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I391" t="n">
@@ -14164,22 +14176,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>NVDA_KZ</t>
+          <t>NNDQ</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>American Depositary Shares of Nanduq PLC</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US74735M1080</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -14189,7 +14201,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I392" t="n">
@@ -14199,22 +14211,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>OKEY</t>
+          <t>NVDA_KZ</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Global Depository Receipts of O'KEY Group S.A.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>US6708662019</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -14224,7 +14236,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I393" t="n">
@@ -14234,22 +14246,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ORCL_KZ</t>
+          <t>OKEY</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ORACLE CORPORATION</t>
+          <t>Global Depository Receipts of O'KEY Group S.A.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>US68389X1054</t>
+          <t>US6708662019</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -14259,7 +14271,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I394" t="n">
@@ -14269,12 +14281,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>OXY_KZ</t>
+          <t>ORCL_KZ</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp.</t>
+          <t>ORACLE CORPORATION</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14284,7 +14296,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>US6745991058</t>
+          <t>US68389X1054</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -14304,12 +14316,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>PFE_KZ</t>
+          <t>OXY_KZ</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Occidental Petroleum Corp.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -14319,7 +14331,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>US7170811035</t>
+          <t>US6745991058</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -14339,12 +14351,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>PHO_KZ</t>
+          <t>PFE_KZ</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Invesco Exchange-Traded Fund Trust</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14354,7 +14366,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>US46137V1420</t>
+          <t>US7170811035</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
@@ -14374,12 +14386,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>PYPL_KZ</t>
+          <t>PHO_KZ</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc.</t>
+          <t>Invesco Exchange-Traded Fund Trust</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14389,7 +14401,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>US70450Y1038</t>
+          <t>US46137V1420</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -14409,12 +14421,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>QCOM_KZ</t>
+          <t>PYPL_KZ</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>QUALCOMM Inc.</t>
+          <t>PayPal Holdings Inc.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14424,7 +14436,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>US7475251036</t>
+          <t>US70450Y1038</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -14444,12 +14456,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>QQQ_KZ</t>
+          <t>QCOM_KZ</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Invesco Exchange-Traded Fund Trust</t>
+          <t>QUALCOMM Inc.</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14459,7 +14471,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>US46090E1038</t>
+          <t>US7475251036</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -14479,12 +14491,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>SBUX_KZ</t>
+          <t>QQQ_KZ</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Invesco Exchange-Traded Fund Trust</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -14494,7 +14506,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>US8552441094</t>
+          <t>US46090E1038</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -14514,12 +14526,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>SLV_KZ</t>
+          <t>SBUX_KZ</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>iShares Silver Trust</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -14529,7 +14541,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>US46428Q1094</t>
+          <t>US8552441094</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -14549,12 +14561,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>SPCX_KZ</t>
+          <t>SLV_KZ</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Space Exploration Technologies Corp.</t>
+          <t>iShares Silver Trust</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -14564,7 +14576,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>US84615Q1031</t>
+          <t>US46428Q1094</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -14584,12 +14596,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>SPY_KZ</t>
+          <t>SPCX_KZ</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>SSGA</t>
+          <t>Space Exploration Technologies Corp.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14599,7 +14611,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>US78462F1030</t>
+          <t>US84615Q1031</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
@@ -14619,12 +14631,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>TLT_KZ</t>
+          <t>SPY_KZ</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>iShares Trust</t>
+          <t>SSGA</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14634,7 +14646,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>US4642874329</t>
+          <t>US78462F1030</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
@@ -14654,12 +14666,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>TSLA_KZ</t>
+          <t>TLT_KZ</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>iShares Trust</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14669,7 +14681,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>US88160R1014</t>
+          <t>US4642874329</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -14689,12 +14701,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>T_KZ</t>
+          <t>TSLA_KZ</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -14704,7 +14716,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>US00206R1023</t>
+          <t>US88160R1014</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
@@ -14724,12 +14736,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>UBER_KZ</t>
+          <t>T_KZ</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc.</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -14739,7 +14751,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>US90353T1007</t>
+          <t>US00206R1023</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
@@ -14759,12 +14771,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>URA_KZ</t>
+          <t>UBER_KZ</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Mirae Asset Global Investments</t>
+          <t>Uber Technologies Inc.</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -14774,7 +14786,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>US37954Y8710</t>
+          <t>US90353T1007</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -14794,22 +14806,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>UZHY010125CH</t>
+          <t>URA_KZ</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>I-RECs of 666 MW Charvak HPP</t>
+          <t>Mirae Asset Global Investments</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>SBRFEEQXBR28</t>
+          <t>US37954Y8710</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
@@ -14819,7 +14831,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I410" t="n">
@@ -14829,22 +14841,22 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>VZ_KZ</t>
+          <t>UZHY010125CH</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>I-RECs of 666 MW Charvak HPP</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>US92343V1044</t>
+          <t>SBRFEEQXBR28</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -14854,7 +14866,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I411" t="n">
@@ -14864,12 +14876,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>XLP_KZ</t>
+          <t>VZ_KZ</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>The Select Sector SPDR Trust</t>
+          <t>Verizon Communications Inc.</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -14879,7 +14891,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>US81369Y3080</t>
+          <t>US92343V1044</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
@@ -14899,7 +14911,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>XLU_KZ</t>
+          <t>XLP_KZ</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -14914,7 +14926,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>US81369Y8865</t>
+          <t>US81369Y3080</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -14934,12 +14946,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>XOM_KZ</t>
+          <t>XLU_KZ</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>The Select Sector SPDR Trust</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14949,7 +14961,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>US30233Q1085</t>
+          <t>US81369Y8865</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -14966,6 +14978,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>XOM_KZ</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>KASE Global</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>US30233Q1085</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>KASE</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kase_aix_pref_yearly.xlsx
+++ b/data/kase_aix_pref_yearly.xlsx
@@ -12056,17 +12056,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>AIRAd / AIRA.Y</t>
+          <t>AIRA.Y</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Эйр Астана / GDRs of Air Astana JSC</t>
+          <t>GDRs of Air Astana JSC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -12074,11 +12074,7 @@
           <t>US0090632078</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>US0090631088</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
         <v>2026</v>
@@ -13048,17 +13044,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>FRHC_KZ / FRHC</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp. / Ordinary shares of Freedom Holding Corp.</t>
+          <t>Ordinary shares of Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>акции / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -13328,17 +13324,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>HSBKd / HSBK.Y</t>
+          <t>HSBK.Y</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Народный Банк Казахстана / GDRs of "Halyk Savings Bank of Kazakhstan" JSC</t>
+          <t>GDRs of "Halyk Savings Bank of Kazakhstan" JSC</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -13346,11 +13342,7 @@
           <t>US46627J3023</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>US46627J2033</t>
-        </is>
-      </c>
+      <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
         <v>2026</v>
@@ -13717,22 +13709,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>KO_KZ</t>
+          <t>KAP.Y</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Global Depository Receipts of NC "Kazatomprom" JSC</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>KASE Global</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US63253R2013</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -13742,7 +13734,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>KASE</t>
+          <t>AIX</t>
         </is>
       </c>
       <c r="I379" t="n">
@@ -13752,36 +13744,32 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>KSPId / KSPI</t>
+          <t>KO_KZ</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Kaspi.kz / AMERICAN DEPOSITORY SHARES OF JSC "KASPI.KZ"</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>KASE Global</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>US48581R2058</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>US48581R1068</t>
-        </is>
-      </c>
+          <t>US1912161007</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
         <v>2026</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>AIX</t>
+          <t>KASE</t>
         </is>
       </c>
       <c r="I380" t="n">
@@ -13791,22 +13779,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>KZAPd / KAP.Y</t>
+          <t>KSPI</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Национальная атомная компания "Казатомпром" / Global Depository Receipts of NC "Kazatomprom" JSC</t>
+          <t>AMERICAN DEPOSITORY SHARES OF JSC "KASPI.KZ"</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>производные ценные бумаги / EQTY</t>
+          <t>EQTY</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>US63253R2013</t>
+          <t>US48581R2058</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
